--- a/docs/table-spec.xlsx
+++ b/docs/table-spec.xlsx
@@ -1645,8 +1645,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">모임 날짜. 시각을 붙이지 않는다 — "8월 14일 회식"은 사람의 표현이지 순간이 아니다. DATETIME 으로 다루면 KST 오전 9시 이전에 만든 모임이 UTC 변환으로 전날이 된다(API.md §0.2)
-</t>
+          <t>모임 날짜. 시각을 붙이지 않는다 — "8월 14일 회식"은 사람의 표현이지 순간이 아니다. DATETIME 으로 다루면 KST 오전 9시 이전에 만든 모임이 UTC 변환으로 전날이 된다(API.md §0.2)</t>
         </is>
       </c>
     </row>
@@ -2226,8 +2225,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">SENT/RECEIVED 로 표시된 시점의 최종 부담액. 자기신고가 아니라 서버가 그 순간 계산해 기록한다. 재정산 차액 계산의 유일한 근거다(SPEC §5-c)
-</t>
+          <t>SENT/RECEIVED 로 표시된 시점의 최종 부담액. 자기신고가 아니라 서버가 그 순간 계산해 기록한다. 재정산 차액 계산의 유일한 근거다(SPEC §5-c)</t>
         </is>
       </c>
     </row>
@@ -2317,8 +2315,7 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">이 참여자가 결제자로 지정됐을 때 받을 계좌의 은행명. 결제자 본인이 직접 등록한다(API.md §5.5) — Gathering 에 두지 않는 이유는 주최자 말고도 받을 사람이 생기기 때문이다(택시비를 다른 사람이 결제한 경우)
-</t>
+          <t>이 참여자가 결제자로 지정됐을 때 받을 계좌의 은행명. 결제자 본인이 직접 등록한다(API.md §5.5) — Gathering 에 두지 않는 이유는 주최자 말고도 받을 사람이 생기기 때문이다(택시비를 다른 사람이 결제한 경우)</t>
         </is>
       </c>
     </row>
@@ -2506,8 +2503,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">차수 순번(정렬용, 표시 라벨과 별개). 서버가 MAX(seq)+1 로 정한다 — 클라이언트가 정하면 동시 추가 때 중복이 난다(API.md §4.1)
-</t>
+          <t>차수 순번(정렬용, 표시 라벨과 별개). 서버가 MAX(seq)+1 로 정한다 — 클라이언트가 정하면 동시 추가 때 중복이 난다(API.md §4.1)</t>
         </is>
       </c>
     </row>
@@ -3821,8 +3817,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">모임 날짜. 시각을 붙이지 않는다 — "8월 14일 회식"은 사람의 표현이지 순간이 아니다. DATETIME 으로 다루면 KST 오전 9시 이전에 만든 모임이 UTC 변환으로 전날이 된다(API.md §0.2)
-</t>
+          <t>모임 날짜. 시각을 붙이지 않는다 — "8월 14일 회식"은 사람의 표현이지 순간이 아니다. DATETIME 으로 다루면 KST 오전 9시 이전에 만든 모임이 UTC 변환으로 전날이 된다(API.md §0.2)</t>
         </is>
       </c>
     </row>
@@ -4128,8 +4123,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">SENT/RECEIVED 로 표시된 시점의 최종 부담액. 자기신고가 아니라 서버가 그 순간 계산해 기록한다. 재정산 차액 계산의 유일한 근거다(SPEC §5-c)
-</t>
+          <t>SENT/RECEIVED 로 표시된 시점의 최종 부담액. 자기신고가 아니라 서버가 그 순간 계산해 기록한다. 재정산 차액 계산의 유일한 근거다(SPEC §5-c)</t>
         </is>
       </c>
     </row>
@@ -4180,8 +4174,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">이 참여자가 결제자로 지정됐을 때 받을 계좌의 은행명. 결제자 본인이 직접 등록한다(API.md §5.5) — Gathering 에 두지 않는 이유는 주최자 말고도 받을 사람이 생기기 때문이다(택시비를 다른 사람이 결제한 경우)
-</t>
+          <t>이 참여자가 결제자로 지정됐을 때 받을 계좌의 은행명. 결제자 본인이 직접 등록한다(API.md §5.5) — Gathering 에 두지 않는 이유는 주최자 말고도 받을 사람이 생기기 때문이다(택시비를 다른 사람이 결제한 경우)</t>
         </is>
       </c>
     </row>
@@ -4283,8 +4276,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">차수 순번(정렬용, 표시 라벨과 별개). 서버가 MAX(seq)+1 로 정한다 — 클라이언트가 정하면 동시 추가 때 중복이 난다(API.md §4.1)
-</t>
+          <t>차수 순번(정렬용, 표시 라벨과 별개). 서버가 MAX(seq)+1 로 정한다 — 클라이언트가 정하면 동시 추가 때 중복이 난다(API.md §4.1)</t>
         </is>
       </c>
     </row>
@@ -5051,8 +5043,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">차수 순번 중복 방지. core Validator 의 DUPLICATE_ROUND_SEQ 와 같은 규칙을 DB 레벨에서도 건다 — 애플리케이션 버그로 뚫려도 여기서 막힌다
-</t>
+          <t>차수 순번 중복 방지. core Validator 의 DUPLICATE_ROUND_SEQ 와 같은 규칙을 DB 레벨에서도 건다 — 애플리케이션 버그로 뚫려도 여기서 막힌다</t>
         </is>
       </c>
     </row>
